--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488170_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488170_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3002</v>
+        <v>1.6913</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9585</v>
+        <v>3.4481</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6583</v>
+        <v>-1.7568</v>
       </c>
       <c r="G2" t="n">
         <v>2.4458</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0943</v>
+        <v>-0.6047</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1693</v>
+        <v>0.0709</v>
       </c>
       <c r="V2" t="n">
         <v>-1.8883</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1114</v>
+        <v>-0.3055</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.333</v>
+        <v>-0.6268</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4444</v>
+        <v>0.3213</v>
       </c>
       <c r="G4" t="n">
         <v>0.5834</v>
@@ -766,13 +766,13 @@
         <v>0.1853</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8991</v>
+        <v>0.4822</v>
       </c>
       <c r="T4" t="n">
-        <v>0.434</v>
+        <v>0.1402</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4651</v>
+        <v>0.342</v>
       </c>
       <c r="V4" t="n">
         <v>-0.63</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3518</v>
+        <v>-0.6954</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4643</v>
+        <v>-1.6602</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1126</v>
+        <v>0.9648</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6004</v>
@@ -844,13 +844,13 @@
         <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5457</v>
+        <v>0.2021</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1131</v>
+        <v>-0.309</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.5111</v>
       </c>
       <c r="V5" t="n">
         <v>0.6294</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TOMAIC TOMAIC</t>
+          <t>J. BARRIENTOS PRIETO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5389</v>
+        <v>-1.4594</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8151</v>
+        <v>1.1747</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.354</v>
+        <v>-2.6342</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3578</v>
+        <v>0.9432</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1765</v>
+        <v>-2.0276</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5342</v>
+        <v>2.9707</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6567</v>
+        <v>3.7018</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8769</v>
+        <v>0.9233</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7798</v>
+        <v>2.7786</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.2989</v>
+        <v>-2.7587</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.0534</v>
+        <v>-2.9508</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2456</v>
+        <v>0.1922</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0382</v>
+        <v>0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8175</v>
+        <v>-1.1117</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7793</v>
+        <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1415</v>
+        <v>-0.2549</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2263</v>
+        <v>-0.1554</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3678</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.5183</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2022</v>
+        <v>-1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2022</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BARRIENTOS PRIETO</t>
+          <t>J. TOMAIC TOMAIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9004</v>
+        <v>-1.7845</v>
       </c>
       <c r="E7" t="n">
-        <v>0.783</v>
+        <v>1.7172</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6834</v>
+        <v>-3.5017</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9432</v>
+        <v>0.3578</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0276</v>
+        <v>-0.1765</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9707</v>
+        <v>0.5342</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7018</v>
+        <v>4.6567</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9233</v>
+        <v>3.8769</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7786</v>
+        <v>0.7798</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7587</v>
+        <v>-4.2989</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.9508</v>
+        <v>-4.0534</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1922</v>
+        <v>-0.2456</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3706</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1117</v>
+        <v>-4.8175</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4823</v>
+        <v>2.7793</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6959</v>
+        <v>-0.1041</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5471</v>
+        <v>-0.3242</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1487</v>
+        <v>0.2201</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5183</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.26</v>
+        <v>2.2022</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2583</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0747</v>
+        <v>-2.0255</v>
       </c>
       <c r="E8" t="n">
         <v>-1.5793</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4955</v>
+        <v>-0.4462</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2359</v>
@@ -1078,13 +1078,13 @@
         <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MEGIAS</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5906</v>
+        <v>-2.072</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9141</v>
+        <v>-1.6118</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6765</v>
+        <v>-0.4602</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4695</v>
+        <v>-2.3318</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5616</v>
+        <v>-3.4117</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9078000000000001</v>
+        <v>1.0799</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7986</v>
+        <v>0.2674</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1979</v>
+        <v>-1.1427</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6007</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6708</v>
+        <v>-2.5991</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3637</v>
+        <v>-2.269</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3071</v>
+        <v>-0.3301</v>
       </c>
       <c r="P9" t="n">
         <v>-0.3706</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2495</v>
+        <v>0.3159</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0037</v>
+        <v>-0.1554</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2532</v>
+        <v>0.4713</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>I. FERNANDEZ MEGIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6607</v>
+        <v>-2.8357</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0035</v>
+        <v>-2.1099</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6572</v>
+        <v>-0.7258</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3318</v>
+        <v>-2.4695</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.4117</v>
+        <v>-1.5616</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0799</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2674</v>
+        <v>-0.7986</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1427</v>
+        <v>-0.1979</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>-0.6007</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5991</v>
+        <v>-1.6708</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.269</v>
+        <v>-1.3637</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3301</v>
+        <v>-0.3071</v>
       </c>
       <c r="P10" t="n">
         <v>-0.3706</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6676</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2728</v>
+        <v>0.0044</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5471</v>
+        <v>-0.1996</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2743</v>
+        <v>0.2039</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. MARKWARDT FERNANDES</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9441</v>
+        <v>-3.6483</v>
       </c>
       <c r="E11" t="n">
-        <v>0.344</v>
+        <v>0.2864</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2881</v>
+        <v>-3.9347</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.0895</v>
+        <v>-0.6414</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.761</v>
+        <v>1.0236</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3286</v>
+        <v>-1.665</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0973</v>
+        <v>1.8589</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0819</v>
+        <v>2.3873</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0154</v>
+        <v>-0.5284</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.9922</v>
+        <v>-2.5003</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.6791</v>
+        <v>-1.3637</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3131</v>
+        <v>-1.1366</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8529</v>
+        <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4778</v>
+        <v>-0.4156</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6266</v>
+        <v>-0.3311</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1487</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-3.1471</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>R. MARKWARDT FERNANDES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2364</v>
+        <v>-4.2659</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2032</v>
+        <v>-1.027</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0332</v>
+        <v>-3.2389</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6414</v>
+        <v>-6.0895</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0236</v>
+        <v>-3.761</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.665</v>
+        <v>-2.3286</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8589</v>
+        <v>-1.0973</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3873</v>
+        <v>-0.0819</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5284</v>
+        <v>-1.0154</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5003</v>
+        <v>-4.9922</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3637</v>
+        <v>-3.6791</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1366</v>
+        <v>-1.3131</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4823</v>
+        <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0038</v>
+        <v>0.1561</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8207</v>
+        <v>0.2556</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1831</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.1471</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.8321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.3371</v>
+        <v>-7.8222</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.54</v>
+        <v>-5.1483</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.797</v>
+        <v>-2.6739</v>
       </c>
       <c r="G13" t="n">
         <v>-4.7745</v>
@@ -1468,13 +1468,13 @@
         <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4127</v>
+        <v>-0.8978</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0396</v>
+        <v>-0.6479</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3731</v>
+        <v>-0.25</v>
       </c>
       <c r="V13" t="n">
         <v>0.6294</v>
@@ -1504,10 +1504,10 @@
         <v>-24.601</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.514699999999999</v>
+        <v>-6.514799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.0862</v>
+        <v>-18.0863</v>
       </c>
       <c r="G14" t="n">
         <v>-13.1907</v>
@@ -1516,7 +1516,7 @@
         <v>-16.8</v>
       </c>
       <c r="I14" t="n">
-        <v>3.609300000000001</v>
+        <v>3.6093</v>
       </c>
       <c r="J14" t="n">
         <v>11.219</v>
@@ -1546,10 +1546,10 @@
         <v>13.8965</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0942</v>
+        <v>-1.094</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.331300000000001</v>
+        <v>-2.3315</v>
       </c>
       <c r="U14" t="n">
         <v>1.2372</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6689</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>9.202500000000001</v>
+        <v>9.4963</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5336</v>
+        <v>-1.1643</v>
       </c>
       <c r="G15" t="n">
         <v>4.8977</v>
@@ -1624,13 +1624,13 @@
         <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2462</v>
+        <v>0.4169</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1604</v>
+        <v>0.4542</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4066</v>
+        <v>-0.0373</v>
       </c>
       <c r="V15" t="n">
         <v>2.8321</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8924</v>
+        <v>5.7557</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9773</v>
+        <v>3.2089</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9152</v>
+        <v>2.5467</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4839</v>
+        <v>4.7156</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1795</v>
+        <v>1.3934</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6956</v>
+        <v>3.3222</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6923</v>
+        <v>4.4513</v>
       </c>
       <c r="K16" t="n">
-        <v>4.0963</v>
+        <v>1.8895</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.404</v>
+        <v>2.5618</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2084</v>
+        <v>0.2643</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.4961</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2915</v>
+        <v>0.7604</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0382</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9646</v>
+        <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3704</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2114</v>
+        <v>-0.3513</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1589</v>
+        <v>0.429</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.8888</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5598</v>
+        <v>5.4252</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0131</v>
+        <v>2.8794</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5467</v>
+        <v>2.5458</v>
       </c>
       <c r="G17" t="n">
-        <v>4.7156</v>
+        <v>2.4839</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3934</v>
+        <v>3.1795</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3222</v>
+        <v>-0.6956</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4513</v>
+        <v>3.6923</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8895</v>
+        <v>4.0963</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5618</v>
+        <v>-0.404</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2643</v>
+        <v>-1.2084</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4961</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7604</v>
+        <v>-0.2915</v>
       </c>
       <c r="P17" t="n">
+        <v>2.0382</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.7793</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.8529</v>
+        <v>2.9646</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1181</v>
+        <v>0.9031</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5471</v>
+        <v>0.1135</v>
       </c>
       <c r="U17" t="n">
-        <v>0.429</v>
+        <v>0.7896</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8888</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0127</v>
+        <v>2.57</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8962</v>
+        <v>0.7982</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1165</v>
+        <v>1.7718</v>
       </c>
       <c r="G18" t="n">
         <v>0.7528</v>
@@ -1858,13 +1858,13 @@
         <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0921</v>
+        <v>0.6494</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2151</v>
+        <v>0.1172</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8769</v>
+        <v>0.5322</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3144</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9342</v>
+        <v>2.0979</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4028</v>
+        <v>2.9573</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5313</v>
+        <v>-0.8595</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1713</v>
+        <v>1.732</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7702</v>
+        <v>1.9394</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.599</v>
+        <v>-0.2074</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6035</v>
+        <v>4.0866</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1735</v>
+        <v>2.6967</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.57</v>
+        <v>1.3899</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4322</v>
+        <v>-2.3545</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4033</v>
+        <v>-0.7573</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.029</v>
+        <v>-1.5973</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7793</v>
+        <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5051</v>
+        <v>-0.0053</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3209</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1843</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2578</v>
+        <v>0.0005</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2578</v>
+        <v>0.6294</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7537</v>
+        <v>2.0398</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8594</v>
+        <v>0.4083</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1057</v>
+        <v>1.6316</v>
       </c>
       <c r="G20" t="n">
-        <v>1.732</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9394</v>
+        <v>0.141</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2074</v>
+        <v>0.5178</v>
       </c>
       <c r="J20" t="n">
-        <v>4.0866</v>
+        <v>0.5481</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6967</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3899</v>
+        <v>0.0415</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3545</v>
+        <v>0.1107</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7573</v>
+        <v>-0.3656</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5973</v>
+        <v>0.4763</v>
       </c>
       <c r="P20" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2234</v>
+        <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3494</v>
+        <v>-0.2484</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0037</v>
+        <v>-0.4722</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3457</v>
+        <v>0.2238</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0005</v>
+        <v>1.2589</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6294</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3767</v>
+        <v>1.2733</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1145</v>
+        <v>-0.2827</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2623</v>
+        <v>1.556</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.1713</v>
       </c>
       <c r="H21" t="n">
-        <v>0.141</v>
+        <v>3.7702</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5178</v>
+        <v>-3.599</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5481</v>
+        <v>1.6035</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5066000000000001</v>
+        <v>4.1735</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0415</v>
+        <v>-2.57</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1107</v>
+        <v>-1.4322</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3656</v>
+        <v>-0.4033</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4763</v>
+        <v>-1.029</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R21" t="n">
-        <v>1.297</v>
+        <v>2.7793</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9115</v>
+        <v>-0.1558</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.766</v>
+        <v>-0.3646</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1455</v>
+        <v>0.2089</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2589</v>
+        <v>1.2578</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2589</v>
+        <v>1.2578</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0048</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-0.1759</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1807</v>
+        <v>0.1069</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7401</v>
@@ -2248,13 +2248,13 @@
         <v>0.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2557</v>
+        <v>-0.3295</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2189</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0368</v>
+        <v>-0.1107</v>
       </c>
       <c r="V23" t="n">
         <v>0.63</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1886</v>
+        <v>-0.1394</v>
       </c>
       <c r="E24" t="n">
         <v>0.4515</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6402</v>
+        <v>-0.5909</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0009</v>
@@ -2326,13 +2326,13 @@
         <v>0.3706</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4472</v>
+        <v>-0.3979</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2189</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2283</v>
+        <v>-0.1791</v>
       </c>
       <c r="V24" t="n">
         <v>1.8888</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1155</v>
+        <v>-1.1183</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6383</v>
+        <v>-0.1486</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4772</v>
+        <v>-0.9697</v>
       </c>
       <c r="G25" t="n">
         <v>0.8638</v>
@@ -2404,13 +2404,13 @@
         <v>1.1117</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3531</v>
+        <v>0.3504</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7113</v>
+        <v>-0.2216</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0644</v>
+        <v>0.572</v>
       </c>
       <c r="V25" t="n">
         <v>-2.5177</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.9201</v>
+        <v>-2.1882</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6389</v>
+        <v>-2.1285</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2812</v>
+        <v>-0.0596</v>
       </c>
       <c r="G26" t="n">
         <v>-0.9663</v>
@@ -2482,13 +2482,13 @@
         <v>2.0382</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1017</v>
+        <v>-0.1663</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3209</v>
+        <v>-0.1688</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2191</v>
+        <v>0.0025</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3144</v>
@@ -2539,7 +2539,7 @@
         <v>22.41409999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>1.9957</v>
+        <v>1.995699999999999</v>
       </c>
       <c r="M27" t="n">
         <v>-11.219</v>
@@ -2551,7 +2551,7 @@
         <v>-5.604900000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>3.705999999999999</v>
+        <v>3.706</v>
       </c>
       <c r="Q27" t="n">
         <v>-13.8964</v>
@@ -2566,7 +2566,7 @@
         <v>-1.2372</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3315</v>
+        <v>2.3314</v>
       </c>
       <c r="V27" t="n">
         <v>6.610400000000001</v>
